--- a/data/trans_dic/IP36A-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP36A-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que perciben algun tipo de pensión</t>
+          <t>Adultos que perciben algun tipo de pensión (tasa de respuesta: 99,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 11,01</t>
+          <t>2,48; 10,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,76; 10,97</t>
+          <t>1,97; 10,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 9,14</t>
+          <t>0,91; 10,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,31; 29,0</t>
+          <t>8,93; 29,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 10,32</t>
+          <t>1,87; 10,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,21; 13,33</t>
+          <t>3,64; 13,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,72; 11,84</t>
+          <t>2,75; 12,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,83; 24,06</t>
+          <t>6,43; 23,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,7; 8,79</t>
+          <t>2,74; 8,87</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,55; 9,6</t>
+          <t>3,6; 9,6</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 8,78</t>
+          <t>2,63; 8,58</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,09; 22,77</t>
+          <t>9,63; 22,52</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 8,54</t>
+          <t>1,46; 8,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,08; 17,34</t>
+          <t>8,39; 17,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,38; 15,09</t>
+          <t>6,68; 15,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,28; 16,98</t>
+          <t>4,24; 16,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,31; 13,03</t>
+          <t>3,91; 12,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,15; 14,72</t>
+          <t>6,01; 14,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,72; 16,17</t>
+          <t>7,07; 16,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,91; 25,55</t>
+          <t>9,88; 24,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,39; 9,5</t>
+          <t>3,67; 9,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,27; 14,95</t>
+          <t>8,51; 14,62</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,49; 13,86</t>
+          <t>7,49; 13,82</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,89; 19,12</t>
+          <t>8,49; 18,23</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,48; 16,19</t>
+          <t>4,7; 15,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,1; 18,09</t>
+          <t>6,77; 18,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,74; 16,09</t>
+          <t>5,33; 15,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,79; 27,67</t>
+          <t>4,93; 27,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,71; 14,75</t>
+          <t>3,72; 14,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,92; 18,16</t>
+          <t>7,36; 18,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,78; 22,54</t>
+          <t>9,11; 22,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,58; 29,91</t>
+          <t>12,03; 30,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,44; 13,23</t>
+          <t>5,73; 13,24</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,49; 16,4</t>
+          <t>8,15; 16,1</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,43; 17,27</t>
+          <t>8,37; 17,42</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,13; 24,71</t>
+          <t>9,04; 25,15</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,48; 20,08</t>
+          <t>6,28; 19,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,86; 15,99</t>
+          <t>5,25; 15,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,96; 14,98</t>
+          <t>4,83; 13,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,57; 34,32</t>
+          <t>15,37; 35,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,89; 13,47</t>
+          <t>2,91; 12,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,36; 16,78</t>
+          <t>6,88; 17,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,11; 26,2</t>
+          <t>11,85; 26,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,39; 35,54</t>
+          <t>15,1; 35,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,29; 13,75</t>
+          <t>5,72; 14,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,49; 14,67</t>
+          <t>7,28; 14,4</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,03; 17,81</t>
+          <t>9,31; 17,98</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,72; 31,95</t>
+          <t>17,86; 31,94</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,2; 10,21</t>
+          <t>5,15; 10,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,89; 12,72</t>
+          <t>7,73; 12,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,21; 11,0</t>
+          <t>6,17; 10,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,3; 21,24</t>
+          <t>10,27; 21,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,17; 9,66</t>
+          <t>4,95; 9,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,96; 12,77</t>
+          <t>7,82; 12,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,59; 15,5</t>
+          <t>9,4; 15,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,33; 23,07</t>
+          <t>14,81; 23,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,78; 9,02</t>
+          <t>5,68; 9,01</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,41; 12,04</t>
+          <t>8,41; 11,84</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,78; 12,64</t>
+          <t>8,7; 12,36</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,56; 20,82</t>
+          <t>13,57; 21,07</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que perciben algun tipo de pensión (tasa de respuesta: 99,16%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3845</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3997</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2868</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8479</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3993</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6653</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>5056</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>6409</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>7838</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>10650</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>7924</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>14888</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1755; 7541</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1606; 8804</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>676; 7792</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4439; 14792</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1428; 8064</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3292; 12010</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2204; 10061</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>3115; 11229</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>4030; 13062</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>6194; 16515</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4065; 13267</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>9446; 22087</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3704</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14745</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11080</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5929</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>7773</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>12432</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>12891</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>13316</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>11477</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>27178</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>23970</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>19245</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1294; 7290</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>9835; 20910</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>7343; 16632</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2760; 10471</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>3949; 12771</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>7610; 18637</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>8565; 20557</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>8010; 19889</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>6971; 17194</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>20762; 35649</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>17313; 31940</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>12417; 26655</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>6036</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9353</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>7618</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>14497</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>5655</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>10845</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>11556</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>12727</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>11691</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>20198</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>19174</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>27224</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>3102; 10499</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5483; 15114</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4121; 12221</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4587; 25846</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2519; 9726</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>6786; 17049</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>7187; 17670</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>7885; 20072</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>7663; 17701</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>14120; 27890</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>13073; 27192</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>14337; 39876</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>8914</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8319</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>12493</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4704</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>11829</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>15173</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>15599</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>13619</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>22230</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>23492</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>28091</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>4780; 14746</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>5477; 16452</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>4604; 13273</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>8056; 18661</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2053; 9066</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>7138; 17892</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>9951; 21912</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>9497; 22276</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>8377; 20729</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>15159; 29960</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>16697; 32235</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>20592; 36823</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>22499</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>38497</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>29884</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>41397</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>22125</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>41758</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>44676</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>48051</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>44624</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>80256</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>74560</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>89448</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>15541; 30403</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>29687; 48926</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>22052; 38235</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>26728; 56756</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>15633; 29705</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>32288; 51979</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>34212; 55659</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>38180; 61063</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>35070; 55613</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>67089; 94406</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>62753; 89150</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>70319; 109177</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP36A-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP36A-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 10,67</t>
+          <t>1,92; 11,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,97; 10,8</t>
+          <t>1,71; 10,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 10,44</t>
+          <t>0,9; 9,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,93; 29,77</t>
+          <t>8,46; 28,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 10,54</t>
+          <t>1,8; 10,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,64; 13,26</t>
+          <t>3,67; 13,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,75; 12,57</t>
+          <t>2,73; 12,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,43; 23,2</t>
+          <t>6,28; 23,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 8,87</t>
+          <t>2,79; 8,64</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,6; 9,6</t>
+          <t>3,44; 9,52</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,63; 8,58</t>
+          <t>2,64; 8,84</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,63; 22,52</t>
+          <t>9,62; 23,42</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 8,21</t>
+          <t>1,44; 9,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,39; 17,83</t>
+          <t>8,01; 17,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,68; 15,13</t>
+          <t>6,1; 15,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,24; 16,08</t>
+          <t>4,89; 16,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,91; 12,66</t>
+          <t>3,94; 12,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,01; 14,72</t>
+          <t>5,86; 14,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,07; 16,97</t>
+          <t>6,81; 15,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,88; 24,53</t>
+          <t>10,17; 25,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,67; 9,06</t>
+          <t>3,64; 9,18</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,51; 14,62</t>
+          <t>8,14; 14,22</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,49; 13,82</t>
+          <t>7,6; 13,96</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,49; 18,23</t>
+          <t>8,97; 19,19</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,7; 15,92</t>
+          <t>4,68; 15,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,77; 18,65</t>
+          <t>6,74; 17,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,33; 15,82</t>
+          <t>5,3; 15,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,93; 27,77</t>
+          <t>5,25; 27,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,72; 14,36</t>
+          <t>3,82; 14,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,36; 18,5</t>
+          <t>6,66; 17,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,11; 22,4</t>
+          <t>9,24; 22,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,03; 30,64</t>
+          <t>11,89; 30,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,73; 13,24</t>
+          <t>5,34; 13,09</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,15; 16,1</t>
+          <t>7,97; 15,81</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,37; 17,42</t>
+          <t>8,17; 16,7</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,04; 25,15</t>
+          <t>9,76; 25,51</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,28; 19,38</t>
+          <t>6,22; 18,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,25; 15,77</t>
+          <t>5,48; 16,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,83; 13,93</t>
+          <t>5,02; 15,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,37; 35,61</t>
+          <t>15,85; 35,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 12,87</t>
+          <t>2,84; 13,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,88; 17,25</t>
+          <t>7,23; 17,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,85; 26,1</t>
+          <t>10,94; 26,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,1; 35,43</t>
+          <t>16,17; 35,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,72; 14,14</t>
+          <t>5,86; 14,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,28; 14,4</t>
+          <t>7,47; 14,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,31; 17,98</t>
+          <t>9,27; 18,08</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,86; 31,94</t>
+          <t>18,46; 32,07</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,15; 10,08</t>
+          <t>5,25; 10,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,73; 12,73</t>
+          <t>7,8; 12,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,17; 10,71</t>
+          <t>6,29; 10,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,27; 21,81</t>
+          <t>10,79; 21,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,95; 9,41</t>
+          <t>5,03; 9,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,82; 12,58</t>
+          <t>7,79; 12,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,4; 15,29</t>
+          <t>9,62; 15,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,81; 23,68</t>
+          <t>14,67; 23,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,68; 9,01</t>
+          <t>5,78; 9,05</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,41; 11,84</t>
+          <t>8,36; 11,97</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,7; 12,36</t>
+          <t>8,53; 12,41</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,57; 21,07</t>
+          <t>13,56; 20,74</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1755; 7541</t>
+          <t>1357; 7817</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1606; 8804</t>
+          <t>1394; 8307</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>676; 7792</t>
+          <t>671; 7184</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4439; 14792</t>
+          <t>4205; 14181</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1428; 8064</t>
+          <t>1379; 8009</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3292; 12010</t>
+          <t>3325; 11977</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2204; 10061</t>
+          <t>2181; 10016</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3115; 11229</t>
+          <t>3041; 11246</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4030; 13062</t>
+          <t>4105; 12716</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6194; 16515</t>
+          <t>5927; 16390</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4065; 13267</t>
+          <t>4079; 13668</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9446; 22087</t>
+          <t>9433; 22976</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1294; 7290</t>
+          <t>1279; 8117</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9835; 20910</t>
+          <t>9392; 20705</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7343; 16632</t>
+          <t>6712; 17028</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2760; 10471</t>
+          <t>3185; 10800</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3949; 12771</t>
+          <t>3972; 12981</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7610; 18637</t>
+          <t>7426; 17952</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8565; 20557</t>
+          <t>8245; 18975</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8010; 19889</t>
+          <t>8250; 21039</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6971; 17194</t>
+          <t>6915; 17414</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20762; 35649</t>
+          <t>19846; 34691</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17313; 31940</t>
+          <t>17556; 32271</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12417; 26655</t>
+          <t>13120; 28055</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3102; 10499</t>
+          <t>3084; 10213</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5483; 15114</t>
+          <t>5461; 13878</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4121; 12221</t>
+          <t>4090; 12259</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4587; 25846</t>
+          <t>4883; 26042</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2519; 9726</t>
+          <t>2584; 9806</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6786; 17049</t>
+          <t>6139; 16419</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7187; 17670</t>
+          <t>7290; 17853</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7885; 20072</t>
+          <t>7792; 19784</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7663; 17701</t>
+          <t>7144; 17491</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14120; 27890</t>
+          <t>13810; 27373</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13073; 27192</t>
+          <t>12749; 26071</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14337; 39876</t>
+          <t>15474; 40449</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4780; 14746</t>
+          <t>4733; 14420</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5477; 16452</t>
+          <t>5723; 17484</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4604; 13273</t>
+          <t>4782; 14372</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8056; 18661</t>
+          <t>8308; 18348</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2053; 9066</t>
+          <t>1999; 9295</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7138; 17892</t>
+          <t>7505; 18177</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9951; 21912</t>
+          <t>9182; 21972</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9497; 22276</t>
+          <t>10170; 22539</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8377; 20729</t>
+          <t>8589; 20823</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15159; 29960</t>
+          <t>15552; 30764</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16697; 32235</t>
+          <t>16613; 32410</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20592; 36823</t>
+          <t>21280; 36978</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15541; 30403</t>
+          <t>15827; 30572</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>29687; 48926</t>
+          <t>29964; 48322</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22052; 38235</t>
+          <t>22450; 38589</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26728; 56756</t>
+          <t>28086; 55108</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15633; 29705</t>
+          <t>15861; 30825</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>32288; 51979</t>
+          <t>32162; 53201</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34212; 55659</t>
+          <t>35004; 55841</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>38180; 61063</t>
+          <t>37838; 60364</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35070; 55613</t>
+          <t>35680; 55861</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>67089; 94406</t>
+          <t>66616; 95421</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>62753; 89150</t>
+          <t>61533; 89457</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>70319; 109177</t>
+          <t>70261; 107481</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP36A-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP36A-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,22%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7,35%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6,32%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14,65%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>5,44%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4,9%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3,84%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17,06%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,22%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,35%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,32%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 11,06</t>
+          <t>1,75; 10,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 10,19</t>
+          <t>4,21; 13,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 9,63</t>
+          <t>2,72; 11,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,46; 28,54</t>
+          <t>7,4; 25,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 10,46</t>
+          <t>2,06; 11,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,67; 13,23</t>
+          <t>1,76; 10,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 12,51</t>
+          <t>0,91; 9,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,28; 23,23</t>
+          <t>9,74; 32,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,79; 8,64</t>
+          <t>2,7; 8,79</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,44; 9,52</t>
+          <t>3,55; 9,6</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 8,84</t>
+          <t>2,73; 8,78</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,62; 23,42</t>
+          <t>9,97; 25,42</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9,82%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10,64%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>17,01%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>4,17%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>12,57%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>10,08%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9,1%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,7%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,82%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>10,64%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 9,14</t>
+          <t>4,31; 13,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,01; 17,66</t>
+          <t>6,15; 14,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,1; 15,49</t>
+          <t>6,72; 16,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,89; 16,59</t>
+          <t>10,07; 26,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,94; 12,86</t>
+          <t>1,44; 8,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,86; 14,18</t>
+          <t>8,08; 17,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,81; 15,66</t>
+          <t>6,38; 15,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,17; 25,95</t>
+          <t>4,36; 17,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,64; 9,18</t>
+          <t>3,39; 9,5</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,14; 14,22</t>
+          <t>8,27; 14,95</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,6; 13,96</t>
+          <t>7,49; 13,86</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,97; 19,19</t>
+          <t>9,64; 19,97</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8,35%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11,77%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>14,65%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>20,04%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>9,15%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>11,54%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>9,86%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>15,58%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8,35%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11,77%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>14,65%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,68; 15,49</t>
+          <t>3,71; 14,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,74; 17,13</t>
+          <t>6,92; 18,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,3; 15,87</t>
+          <t>8,78; 22,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,25; 27,98</t>
+          <t>12,02; 30,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,82; 14,48</t>
+          <t>4,48; 16,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,66; 17,82</t>
+          <t>7,1; 18,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,24; 22,64</t>
+          <t>5,74; 16,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,89; 30,2</t>
+          <t>11,89; 29,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,34; 13,09</t>
+          <t>5,44; 13,23</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,97; 15,81</t>
+          <t>8,49; 16,4</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,17; 16,7</t>
+          <t>8,43; 17,27</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,76; 25,51</t>
+          <t>13,9; 26,84</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6,68%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11,4%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18,08%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>24,34%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>11,72%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>9,97%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>8,73%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>23,84%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,68%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11,4%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>18,08%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,22%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,22; 18,95</t>
+          <t>2,89; 13,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,48; 16,75</t>
+          <t>6,36; 16,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,02; 15,08</t>
+          <t>12,11; 26,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,85; 35,01</t>
+          <t>16,18; 35,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,84; 13,19</t>
+          <t>5,48; 20,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,23; 17,52</t>
+          <t>5,86; 15,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,94; 26,17</t>
+          <t>4,96; 14,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,17; 35,85</t>
+          <t>14,88; 34,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,86; 14,21</t>
+          <t>5,29; 13,75</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,47; 14,78</t>
+          <t>7,49; 14,67</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,27; 18,08</t>
+          <t>9,03; 17,81</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,46; 32,07</t>
+          <t>17,76; 32,23</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7,01%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10,11%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>12,27%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>19,23%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>7,46%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>10,02%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>8,37%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>15,91%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>7,01%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>10,11%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>12,27%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>18,47%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,25; 10,14</t>
+          <t>5,17; 9,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,8; 12,58</t>
+          <t>7,96; 12,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,29; 10,81</t>
+          <t>9,59; 15,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,79; 21,17</t>
+          <t>14,87; 23,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,03; 9,77</t>
+          <t>5,2; 10,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,79; 12,88</t>
+          <t>7,89; 12,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,62; 15,34</t>
+          <t>6,21; 11,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,67; 23,41</t>
+          <t>13,38; 22,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,78; 9,05</t>
+          <t>5,78; 9,02</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,36; 11,97</t>
+          <t>8,41; 12,04</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,53; 12,41</t>
+          <t>8,78; 12,64</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,56; 20,74</t>
+          <t>15,45; 21,98</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1514,37 +1514,37 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3993</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6653</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5056</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5961</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>3845</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>3997</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>2868</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8479</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3993</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6653</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>5056</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>9518</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14888</t>
+          <t>15479</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1357; 7817</t>
+          <t>1336; 7895</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1394; 8307</t>
+          <t>3811; 12068</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>671; 7184</t>
+          <t>2175; 9482</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4205; 14181</t>
+          <t>3010; 10456</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1379; 8009</t>
+          <t>1455; 7778</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3325; 11977</t>
+          <t>1437; 8942</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2181; 10016</t>
+          <t>677; 6818</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3041; 11246</t>
+          <t>5066; 16956</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4105; 12716</t>
+          <t>3968; 12944</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5927; 16390</t>
+          <t>6102; 16522</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4079; 13668</t>
+          <t>4230; 13580</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9433; 22976</t>
+          <t>9243; 23570</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7773</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12432</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12891</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>12867</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>3704</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>14745</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>11080</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5929</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7773</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12432</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>12891</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13316</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19245</t>
+          <t>18691</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1279; 8117</t>
+          <t>4346; 13151</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9392; 20705</t>
+          <t>7788; 18636</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6712; 17028</t>
+          <t>8142; 19586</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3185; 10800</t>
+          <t>7616; 19855</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3972; 12981</t>
+          <t>1283; 7589</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7426; 17952</t>
+          <t>9476; 20328</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8245; 18975</t>
+          <t>7018; 16598</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8250; 21039</t>
+          <t>2602; 10336</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6915; 17414</t>
+          <t>6438; 18028</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19846; 34691</t>
+          <t>20180; 36468</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17556; 32271</t>
+          <t>17308; 32022</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13120; 28055</t>
+          <t>13038; 27011</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>5655</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10845</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>11556</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>6036</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>9353</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>7618</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>14497</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>5655</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>10845</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>11556</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12727</t>
+          <t>11737</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27224</t>
+          <t>23838</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3084; 10213</t>
+          <t>2513; 9992</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5461; 13878</t>
+          <t>6375; 16736</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4090; 12259</t>
+          <t>6921; 17779</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4883; 26042</t>
+          <t>7259; 18689</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2584; 9806</t>
+          <t>2952; 10674</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6139; 16419</t>
+          <t>5754; 14662</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7290; 17853</t>
+          <t>4430; 12431</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7792; 19784</t>
+          <t>7235; 18081</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7144; 17491</t>
+          <t>7266; 17684</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13810; 27373</t>
+          <t>14700; 28408</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12749; 26071</t>
+          <t>13164; 26967</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15474; 40449</t>
+          <t>16853; 32529</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4704</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11829</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>15173</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>14502</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>8914</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>10402</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>8319</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>12493</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4704</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>11829</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>15173</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>15599</t>
+          <t>12858</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>28091</t>
+          <t>27359</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4733; 14420</t>
+          <t>2040; 9488</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5723; 17484</t>
+          <t>6602; 17413</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4782; 14372</t>
+          <t>10167; 21996</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8308; 18348</t>
+          <t>9636; 20891</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1999; 9295</t>
+          <t>4167; 15282</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7505; 18177</t>
+          <t>6114; 16685</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9182; 21972</t>
+          <t>4728; 14281</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10170; 22539</t>
+          <t>7944; 18221</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8589; 20823</t>
+          <t>7759; 20157</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15552; 30764</t>
+          <t>15581; 30527</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16613; 32410</t>
+          <t>16191; 31920</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21280; 36978</t>
+          <t>20064; 36402</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>56</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>22125</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>41758</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>44676</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>45431</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>22499</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>38497</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>29884</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>41397</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>22125</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>41758</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>44676</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>48051</t>
+          <t>39937</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89448</t>
+          <t>85368</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15827; 30572</t>
+          <t>16332; 30481</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>29964; 48322</t>
+          <t>32893; 52758</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22450; 38589</t>
+          <t>34909; 56409</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28086; 55108</t>
+          <t>35136; 56314</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15861; 30825</t>
+          <t>15685; 30786</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>32162; 53201</t>
+          <t>30332; 48868</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35004; 55841</t>
+          <t>22178; 39283</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>37838; 60364</t>
+          <t>30227; 51476</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35680; 55861</t>
+          <t>35697; 55657</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>66616; 95421</t>
+          <t>67069; 96012</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>61533; 89457</t>
+          <t>63317; 91117</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>70261; 107481</t>
+          <t>71378; 101591</t>
         </is>
       </c>
     </row>
